--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>155</v>
+        <v>253</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>146</v>
+        <v>221</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="J11" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K11" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="L11" s="12" t="n">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -928,13 +928,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -845,7 +845,7 @@
         <v>192</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.03125</v>
+        <v>6</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -871,19 +871,19 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J12" s="12" t="n">
         <v>4</v>
@@ -892,7 +892,7 @@
         <v>11</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -928,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -864,7 +864,11 @@
           <t>UDINE</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J11" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K11" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="L11" s="12" t="n">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
@@ -896,14 +896,14 @@
         <v>13</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>193</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>184</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N13" headerRowCount="1">
-  <autoFilter ref="A10:N13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N14" headerRowCount="1">
+  <autoFilter ref="A10:N14"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,11 +520,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -673,7 +673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>206</v>
@@ -961,6 +961,60 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>14289</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SAN DANIELE DEL FRIULI</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>FELICI FILIPPO</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N14" headerRowCount="1">
-  <autoFilter ref="A10:N14"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O14" headerRowCount="1">
+  <autoFilter ref="A10:O14"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIALE VENEZIA 46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>323</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>283</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>111</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>249</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIALE MONSIGNORE GIUSEPPE NOGARA 92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F12" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="M12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>VIALE TRICESIMO 93</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J13" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="M13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -974,17 +1005,19 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>VIA VENEZIA SS 463 KM. 17+262 89/91</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F14" s="12" t="n">
         <v>0</v>
       </c>
@@ -1009,7 +1042,10 @@
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>6</v>
@@ -922,14 +922,14 @@
         <v>13</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K13" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="N13" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N13" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA VENEZIA SS 463 KM. 17+262 89/91</t>
+          <t>VIA VENEZIA, 89/91</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1019,22 +1019,22 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
@@ -922,10 +922,10 @@
         <v>13</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>1</v>
@@ -1019,22 +1019,22 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>7</v>
@@ -922,14 +922,14 @@
         <v>14</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>45</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,22 +1019,22 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>433</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>363</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>23</v>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>9</v>
@@ -922,14 +922,14 @@
         <v>14</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>285</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>266</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>38</v>
-      </c>
       <c r="K13" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1040,14 +1040,14 @@
         <v>0</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>46</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>23</v>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I13" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L13" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="J13" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="M13" s="12" t="n">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,22 +1019,22 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - FELICI FILIPPO.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -684,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>46</v>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>10</v>
@@ -922,14 +922,14 @@
         <v>14</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         <v>11</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>21</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>5</v>
